--- a/ig/main/StructureDefinition-EyeColor.xlsx
+++ b/ig/main/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T12:25:10+00:00</t>
+    <t>2023-05-05T12:31:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-EyeColor.xlsx
+++ b/ig/main/StructureDefinition-EyeColor.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/documentation/StructureDefinition/EyeColor</t>
+    <t>https://interop.esante.gouv.fr/ig/documentation/StructureDefinition/EyeColor</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T12:31:03+00:00</t>
+    <t>2023-05-05T12:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,7 +352,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/documentation/ValueSet/EyeColorVS</t>
+    <t>https://interop.esante.gouv.fr/ig/documentation/ValueSet/EyeColorVS</t>
   </si>
 </sst>
 </file>
@@ -680,7 +680,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.90625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-EyeColor.xlsx
+++ b/ig/main/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T12:37:02+00:00</t>
+    <t>2023-05-05T12:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-EyeColor.xlsx
+++ b/ig/main/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T12:42:02+00:00</t>
+    <t>2023-05-05T15:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-EyeColor.xlsx
+++ b/ig/main/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T15:28:59+00:00</t>
+    <t>2023-05-05T15:37:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-EyeColor.xlsx
+++ b/ig/main/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T15:37:22+00:00</t>
+    <t>2023-05-09T15:39:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-EyeColor.xlsx
+++ b/ig/main/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:39:49+00:00</t>
+    <t>2023-05-09T15:41:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-EyeColor.xlsx
+++ b/ig/main/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:41:54+00:00</t>
+    <t>2023-05-12T16:28:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-EyeColor.xlsx
+++ b/ig/main/StructureDefinition-EyeColor.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T16:28:07+00:00</t>
+    <t>2023-05-17T08:40:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
